--- a/2025-EyL-julio/reporte_general_asistencia.xlsx
+++ b/2025-EyL-julio/reporte_general_asistencia.xlsx
@@ -623,8 +623,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C89D2D723E31AD49A99754977A535CD5" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b5a109aae62f55ade22a1ebca526fb1a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90a45df5-754a-416f-a615-16c5d1ea499f" xmlns:ns3="6a760d76-56c9-4564-aaf3-217c3e3877a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a54c950cadc0d3a3bebfb50cb1316dde" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C89D2D723E31AD49A99754977A535CD5" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b6623b76def32f3ef06c2a4b0e561560">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90a45df5-754a-416f-a615-16c5d1ea499f" xmlns:ns3="6a760d76-56c9-4564-aaf3-217c3e3877a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f1ff2173eaed0aec3757efb91e720664" ns2:_="" ns3:_="">
     <xsd:import namespace="90a45df5-754a-416f-a615-16c5d1ea499f"/>
     <xsd:import namespace="6a760d76-56c9-4564-aaf3-217c3e3877a9"/>
     <xsd:element name="properties">
@@ -643,6 +643,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:Descripcion" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -700,6 +701,13 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Descripcion" ma:index="19" nillable="true" ma:displayName="Descripcion" ma:format="Dropdown" ma:internalName="Descripcion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -833,12 +841,13 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="90a45df5-754a-416f-a615-16c5d1ea499f">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <Descripcion xmlns="90a45df5-754a-416f-a615-16c5d1ea499f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB73E597-BF64-455E-82F0-1949C004ABBA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F7B1EC1-FA54-41A4-AF74-A66481238D89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
